--- a/data/trans_orig/P39B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39B-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2012 (tasa de respuesta: 97,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67597</t>
+          <t>66598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>35384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63558</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80768</t>
+          <t>80079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121777</t>
+          <t>122138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116177</t>
+          <t>116220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159071</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120706</t>
+          <t>120560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167246</t>
+          <t>167978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251714</t>
+          <t>249884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>313097</t>
+          <t>314351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>209008</t>
+          <t>212115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>264049</t>
+          <t>262839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>314842</t>
+          <t>313870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>376352</t>
+          <t>376366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>538274</t>
+          <t>537062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>616487</t>
+          <t>617185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103929</t>
+          <t>100337</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148231</t>
+          <t>145410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193992</t>
+          <t>194161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249530</t>
+          <t>247233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309287</t>
+          <t>311912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380216</t>
+          <t>383983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243692</t>
+          <t>244065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299375</t>
+          <t>299892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413953</t>
+          <t>411492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480180</t>
+          <t>481380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675869</t>
+          <t>674525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>762281</t>
+          <t>762505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128366</t>
+          <t>130141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175849</t>
+          <t>177251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94559</t>
+          <t>95275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140856</t>
+          <t>139674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238697</t>
+          <t>236968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301795</t>
+          <t>300776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365956</t>
+          <t>369550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438442</t>
+          <t>439947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320577</t>
+          <t>321851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>386399</t>
+          <t>387431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>705450</t>
+          <t>702031</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804795</t>
+          <t>804801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>448662</t>
+          <t>450582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>522810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>384379</t>
+          <t>385720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>458357</t>
+          <t>457112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>852828</t>
+          <t>852087</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>953193</t>
+          <t>955164</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191711</t>
+          <t>192103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155676</t>
+          <t>153843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205022</t>
+          <t>207959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>310861</t>
+          <t>308377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384356</t>
+          <t>383543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239702</t>
+          <t>236460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301144</t>
+          <t>299273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335966</t>
+          <t>339190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>408157</t>
+          <t>408858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594179</t>
+          <t>593671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>685551</t>
+          <t>687443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70775</t>
+          <t>71520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72223</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>112140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86180</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126641</t>
+          <t>122983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80782</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116737</t>
+          <t>115439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177992</t>
+          <t>177686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229704</t>
+          <t>230659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115559</t>
+          <t>117228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159186</t>
+          <t>159633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135630</t>
+          <t>135828</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177675</t>
+          <t>178977</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264062</t>
+          <t>262793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>323270</t>
+          <t>323375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65553</t>
+          <t>64192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26093</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50648</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69213</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107917</t>
+          <t>107763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>73157</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52675</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84100</t>
+          <t>84839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104586</t>
+          <t>102092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145571</t>
+          <t>145611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>230656</t>
+          <t>228957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296989</t>
+          <t>291569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167462</t>
+          <t>172500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>227441</t>
+          <t>228224</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>414186</t>
+          <t>413632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>503925</t>
+          <t>500396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597534</t>
+          <t>600090</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>693831</t>
+          <t>693151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>550818</t>
+          <t>546603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>642197</t>
+          <t>640040</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1175442</t>
+          <t>1177852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1302680</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>810867</t>
+          <t>807811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>914329</t>
+          <t>913781</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>872082</t>
+          <t>869059</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>971424</t>
+          <t>970773</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1700006</t>
+          <t>1704494</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1853652</t>
+          <t>1846934</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>299554</t>
+          <t>300159</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>372040</t>
+          <t>375343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>399173</t>
+          <t>400803</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>479134</t>
+          <t>483322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>723585</t>
+          <t>725224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>825844</t>
+          <t>830545</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>552484</t>
+          <t>552902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>642192</t>
+          <t>643236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>835379</t>
+          <t>831146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>937710</t>
+          <t>937734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1418140</t>
+          <t>1413684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1554147</t>
+          <t>1547543</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2016 (tasa de respuesta: 96,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51833</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82079</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>30895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58143</t>
+          <t>59148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90792</t>
+          <t>89904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131535</t>
+          <t>131146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>108144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145828</t>
+          <t>146604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147863</t>
+          <t>148627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196684</t>
+          <t>199689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>268465</t>
+          <t>267696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>332404</t>
+          <t>332955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>176454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221657</t>
+          <t>221080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253756</t>
+          <t>251279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314839</t>
+          <t>312169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444252</t>
+          <t>444708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>516146</t>
+          <t>517743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88934</t>
+          <t>86219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122720</t>
+          <t>125021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154726</t>
+          <t>156016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204789</t>
+          <t>205427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>256711</t>
+          <t>258191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316832</t>
+          <t>316278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132193</t>
+          <t>132265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174067</t>
+          <t>178864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>205478</t>
+          <t>207555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263019</t>
+          <t>261532</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354675</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419752</t>
+          <t>419375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159877</t>
+          <t>162732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211232</t>
+          <t>213626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128741</t>
+          <t>132818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178809</t>
+          <t>181667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306886</t>
+          <t>307004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>374636</t>
+          <t>377155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429419</t>
+          <t>428106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504188</t>
+          <t>502328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446530</t>
+          <t>443772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519450</t>
+          <t>518881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895082</t>
+          <t>895270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>996462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>440542</t>
+          <t>441036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>518373</t>
+          <t>515973</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>463201</t>
+          <t>463534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>538036</t>
+          <t>542140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>928425</t>
+          <t>930195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1035761</t>
+          <t>1032663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175833</t>
+          <t>176026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232328</t>
+          <t>231165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173746</t>
+          <t>171279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>226201</t>
+          <t>226765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363486</t>
+          <t>362235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>440914</t>
+          <t>445524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202727</t>
+          <t>203973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259066</t>
+          <t>258440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275922</t>
+          <t>275329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339961</t>
+          <t>339466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>494990</t>
+          <t>495169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578205</t>
+          <t>578843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70475</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24087</t>
+          <t>24546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47996</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71447</t>
+          <t>72744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110107</t>
+          <t>110224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111856</t>
+          <t>111434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152998</t>
+          <t>150781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115943</t>
+          <t>117700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153489</t>
+          <t>154186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239430</t>
+          <t>240567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>294452</t>
+          <t>296479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98333</t>
+          <t>97685</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135112</t>
+          <t>135437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126793</t>
+          <t>126968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168309</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231823</t>
+          <t>232784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>288308</t>
+          <t>290871</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65665</t>
+          <t>64446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80466</t>
+          <t>79740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93577</t>
+          <t>94485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133825</t>
+          <t>135192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61787</t>
+          <t>60863</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95434</t>
+          <t>95121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>54567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85947</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125269</t>
+          <t>122543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170494</t>
+          <t>166642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>278232</t>
+          <t>275855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>346173</t>
+          <t>343351</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204271</t>
+          <t>204006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262997</t>
+          <t>266616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>498228</t>
+          <t>496673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>590923</t>
+          <t>591517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>675361</t>
+          <t>676918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>771009</t>
+          <t>770529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>743314</t>
+          <t>745022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840509</t>
+          <t>839246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1448140</t>
+          <t>1447935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1573670</t>
+          <t>1574528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>740348</t>
+          <t>741992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>837999</t>
+          <t>840965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,82 +5978,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>928719</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>878080</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>981165</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>29,26%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1629</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1720049</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1654194</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1791263</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>31,76%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>866</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>928719</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>876654</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>981440</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>29,21%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1629</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1720049</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1650041</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1784497</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>29,26%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>324768</t>
+          <t>322763</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>399048</t>
+          <t>395896</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,82 +6091,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>15,01%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>441592</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>399993</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>480563</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>799990</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>748592</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>853289</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>15,13%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>441592</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>399338</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>485947</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>799990</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>751135</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>854130</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>420384</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>499815</t>
+          <t>503033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>560467</t>
+          <t>563719</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>650934</t>
+          <t>653035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1013198</t>
+          <t>1005840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1131952</t>
+          <t>1133145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2023 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>45533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49810</t>
+          <t>49684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76559</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76642</t>
+          <t>77348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110291</t>
+          <t>110490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112147</t>
+          <t>110807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144182</t>
+          <t>143287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197116</t>
+          <t>197958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242415</t>
+          <t>242775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>96887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130374</t>
+          <t>129614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>189088</t>
+          <t>191012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223632</t>
+          <t>224742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>295950</t>
+          <t>293289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>347928</t>
+          <t>340936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85026</t>
+          <t>85622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117594</t>
+          <t>118552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131776</t>
+          <t>131750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161166</t>
+          <t>162315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224935</t>
+          <t>227609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271620</t>
+          <t>273612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100399</t>
+          <t>99559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131809</t>
+          <t>132688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>178019</t>
+          <t>176033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216267</t>
+          <t>215108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>286068</t>
+          <t>287211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337694</t>
+          <t>333778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120908</t>
+          <t>120900</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177165</t>
+          <t>178249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97933</t>
+          <t>101287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170161</t>
+          <t>171808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238043</t>
+          <t>228523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332280</t>
+          <t>331625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401165</t>
+          <t>403911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>483476</t>
+          <t>488124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>288176</t>
+          <t>280846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495035</t>
+          <t>498727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>719071</t>
+          <t>686993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>953385</t>
+          <t>942233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>437616</t>
+          <t>439488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>519002</t>
+          <t>520644</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>554110</t>
+          <t>550694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1141180</t>
+          <t>1117043</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1019414</t>
+          <t>1031692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1598917</t>
+          <t>1669641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221494</t>
+          <t>220897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280248</t>
+          <t>280394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151055</t>
+          <t>165445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275361</t>
+          <t>277421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>389552</t>
+          <t>388092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536127</t>
+          <t>534545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228923</t>
+          <t>233107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289602</t>
+          <t>289083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227199</t>
+          <t>230083</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387422</t>
+          <t>391915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>487099</t>
+          <t>479764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>655704</t>
+          <t>650673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46317</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51605</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>90740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120973</t>
+          <t>117491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161216</t>
+          <t>160760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120699</t>
+          <t>121224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>157771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250682</t>
+          <t>251978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306107</t>
+          <t>310977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157496</t>
+          <t>155405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201940</t>
+          <t>201230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163591</t>
+          <t>164680</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202890</t>
+          <t>201189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>328718</t>
+          <t>326813</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>388969</t>
+          <t>389063</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70910</t>
+          <t>71528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105583</t>
+          <t>106095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82242</t>
+          <t>81731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112710</t>
+          <t>111715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162970</t>
+          <t>161458</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206490</t>
+          <t>211061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78188</t>
+          <t>79271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114894</t>
+          <t>113937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114709</t>
+          <t>113372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151099</t>
+          <t>149443</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200072</t>
+          <t>202230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253284</t>
+          <t>256048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183514</t>
+          <t>182664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>250614</t>
+          <t>246138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162897</t>
+          <t>163118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238945</t>
+          <t>238021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369330</t>
+          <t>369171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464017</t>
+          <t>468492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>627365</t>
+          <t>621943</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>723771</t>
+          <t>724347</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>553754</t>
+          <t>539728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>762029</t>
+          <t>760157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1207471</t>
+          <t>1201260</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1447677</t>
+          <t>1443723</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>722048</t>
+          <t>720647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>820576</t>
+          <t>819309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>940881</t>
+          <t>941356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1546766</t>
+          <t>1615421</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1706566</t>
+          <t>1706057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2312872</t>
+          <t>2386762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>402239</t>
+          <t>399056</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>477180</t>
+          <t>475463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>381171</t>
+          <t>367927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>525548</t>
+          <t>525659</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>801552</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>978567</t>
+          <t>979321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>436015</t>
+          <t>432255</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>512323</t>
+          <t>506763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>512700</t>
+          <t>511344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>720679</t>
+          <t>721810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>989165</t>
+          <t>1001107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1201643</t>
+          <t>1198857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39B-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38974</t>
+          <t>38623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66598</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64052</t>
+          <t>64132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80079</t>
+          <t>80806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122138</t>
+          <t>122383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>118643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159364</t>
+          <t>159565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120560</t>
+          <t>121424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167978</t>
+          <t>169064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>249884</t>
+          <t>249852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314351</t>
+          <t>313069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212115</t>
+          <t>208965</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>262839</t>
+          <t>264496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313870</t>
+          <t>309047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>376366</t>
+          <t>374022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>537062</t>
+          <t>536533</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>617185</t>
+          <t>620710</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100337</t>
+          <t>105028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145410</t>
+          <t>145422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194161</t>
+          <t>193624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247233</t>
+          <t>249263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311912</t>
+          <t>311497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383983</t>
+          <t>380438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244065</t>
+          <t>243156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299892</t>
+          <t>301018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411492</t>
+          <t>413463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481380</t>
+          <t>482077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674525</t>
+          <t>672371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>762505</t>
+          <t>760384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130141</t>
+          <t>131899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177251</t>
+          <t>178158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>96406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139674</t>
+          <t>137916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236968</t>
+          <t>235059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300776</t>
+          <t>297212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>369550</t>
+          <t>364858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>439947</t>
+          <t>435142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321851</t>
+          <t>321604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>387431</t>
+          <t>389167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>702031</t>
+          <t>707623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804801</t>
+          <t>807461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>450582</t>
+          <t>446509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>522810</t>
+          <t>522151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>385720</t>
+          <t>385992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>457112</t>
+          <t>457529</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>852087</t>
+          <t>853542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>955164</t>
+          <t>953263</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138200</t>
+          <t>141929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192103</t>
+          <t>192389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153843</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207959</t>
+          <t>205507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308377</t>
+          <t>310492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383543</t>
+          <t>382162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236460</t>
+          <t>237195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299273</t>
+          <t>300559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339190</t>
+          <t>338170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>408858</t>
+          <t>406126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>593671</t>
+          <t>588978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>687443</t>
+          <t>681612</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>41168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24322</t>
+          <t>24317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>71369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112140</t>
+          <t>109342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>87245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122983</t>
+          <t>124804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79059</t>
+          <t>79671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115439</t>
+          <t>115125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177686</t>
+          <t>175901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230659</t>
+          <t>227080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117228</t>
+          <t>115688</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159633</t>
+          <t>157558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135828</t>
+          <t>134767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>178977</t>
+          <t>176991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>262793</t>
+          <t>263668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>323375</t>
+          <t>322891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36706</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64192</t>
+          <t>65770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>50048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70123</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107763</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44033</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73157</t>
+          <t>71383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84839</t>
+          <t>82691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102092</t>
+          <t>104704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145611</t>
+          <t>146562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228957</t>
+          <t>224232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>291569</t>
+          <t>289578</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172500</t>
+          <t>172871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228224</t>
+          <t>228995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>413632</t>
+          <t>412260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500396</t>
+          <t>501124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600090</t>
+          <t>598277</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>693151</t>
+          <t>688280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546603</t>
+          <t>548511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>640040</t>
+          <t>641371</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1177852</t>
+          <t>1176704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1304535</t>
+          <t>1307470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>807811</t>
+          <t>806157</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>913781</t>
+          <t>910626</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>869059</t>
+          <t>863752</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>970773</t>
+          <t>968473</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1704494</t>
+          <t>1712640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1846934</t>
+          <t>1854880</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>300159</t>
+          <t>300379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>375343</t>
+          <t>376937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>400803</t>
+          <t>399244</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>483322</t>
+          <t>478037</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>725224</t>
+          <t>721689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>830545</t>
+          <t>830635</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>552902</t>
+          <t>549984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>643236</t>
+          <t>638605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>831146</t>
+          <t>833310</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>937734</t>
+          <t>937160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1413684</t>
+          <t>1417961</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1547543</t>
+          <t>1551098</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51207</t>
+          <t>52764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>82477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89904</t>
+          <t>91535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131146</t>
+          <t>131633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108144</t>
+          <t>106842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146604</t>
+          <t>147353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148627</t>
+          <t>148206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199689</t>
+          <t>198813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267696</t>
+          <t>270246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>332955</t>
+          <t>334339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176454</t>
+          <t>174172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221080</t>
+          <t>220812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251279</t>
+          <t>252637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312169</t>
+          <t>311286</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444708</t>
+          <t>438375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>517743</t>
+          <t>515435</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>88858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125021</t>
+          <t>123987</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156016</t>
+          <t>156301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205427</t>
+          <t>205878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258191</t>
+          <t>257335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316278</t>
+          <t>318254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132265</t>
+          <t>133332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178864</t>
+          <t>175649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207555</t>
+          <t>204377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261532</t>
+          <t>257625</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346941</t>
+          <t>352815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419375</t>
+          <t>424248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162732</t>
+          <t>161247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213626</t>
+          <t>212819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132818</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181667</t>
+          <t>178437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>307004</t>
+          <t>307926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377155</t>
+          <t>380789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>428106</t>
+          <t>429037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>502328</t>
+          <t>501482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443772</t>
+          <t>447154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518881</t>
+          <t>520501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895270</t>
+          <t>899529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>996462</t>
+          <t>1003371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>441036</t>
+          <t>442841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>515973</t>
+          <t>514441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>463534</t>
+          <t>461688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542140</t>
+          <t>537793</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>930195</t>
+          <t>928009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1032663</t>
+          <t>1031709</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176026</t>
+          <t>174560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231165</t>
+          <t>230034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171279</t>
+          <t>173055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>226765</t>
+          <t>229481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,47 +4762,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>401003</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>361874</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>442190</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>13,8%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>401003</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>362235</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>445524</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203973</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258440</t>
+          <t>258899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275329</t>
+          <t>276108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339466</t>
+          <t>336893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>495169</t>
+          <t>492045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578843</t>
+          <t>580848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>42244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70972</t>
+          <t>71263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24546</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46199</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72744</t>
+          <t>70875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110224</t>
+          <t>107988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111434</t>
+          <t>112775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150781</t>
+          <t>151718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117700</t>
+          <t>115637</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154186</t>
+          <t>153672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240567</t>
+          <t>239298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>296479</t>
+          <t>295217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97685</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135437</t>
+          <t>134418</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126968</t>
+          <t>127734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>166213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>232784</t>
+          <t>231733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>290871</t>
+          <t>288005</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>36838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64446</t>
+          <t>66353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48796</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79740</t>
+          <t>78838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94485</t>
+          <t>92992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135192</t>
+          <t>136343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60863</t>
+          <t>61373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>96285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54567</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86010</t>
+          <t>86499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122543</t>
+          <t>125898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166642</t>
+          <t>169784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>275855</t>
+          <t>272936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>343351</t>
+          <t>341429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204006</t>
+          <t>203437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266616</t>
+          <t>262845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>496673</t>
+          <t>496333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>591517</t>
+          <t>587252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>676918</t>
+          <t>673978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>770529</t>
+          <t>767289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>745022</t>
+          <t>742979</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>839246</t>
+          <t>845044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1447935</t>
+          <t>1443439</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1574528</t>
+          <t>1577445</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>741992</t>
+          <t>744664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>840965</t>
+          <t>838977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>878080</t>
+          <t>871597</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>981165</t>
+          <t>980900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1654194</t>
+          <t>1649792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1791263</t>
+          <t>1790552</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322763</t>
+          <t>325076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395896</t>
+          <t>395731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>399993</t>
+          <t>405879</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>480563</t>
+          <t>482321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>748592</t>
+          <t>747140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>853289</t>
+          <t>851897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420384</t>
+          <t>422822</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>503033</t>
+          <t>500354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>563719</t>
+          <t>560949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>653035</t>
+          <t>654780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1005840</t>
+          <t>1006547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1133145</t>
+          <t>1129916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>38861</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45533</t>
+          <t>52888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28668</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38334</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61622</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49684</t>
+          <t>56524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>86239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77348</t>
+          <t>85720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110490</t>
+          <t>121075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126988</t>
+          <t>137831</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110807</t>
+          <t>120503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143287</t>
+          <t>156363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>219179</t>
+          <t>240720</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197958</t>
+          <t>216574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242775</t>
+          <t>262895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113560</t>
+          <t>126043</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96887</t>
+          <t>109017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129614</t>
+          <t>145716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>206593</t>
+          <t>230457</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>191012</t>
+          <t>211381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>224742</t>
+          <t>249328</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>320153</t>
+          <t>356499</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>293289</t>
+          <t>332519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>340936</t>
+          <t>385308</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>100715</t>
+          <t>107156</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85622</t>
+          <t>91003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118552</t>
+          <t>125820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>146473</t>
+          <t>159613</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131750</t>
+          <t>143018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162315</t>
+          <t>175513</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>247187</t>
+          <t>266769</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227609</t>
+          <t>244069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273612</t>
+          <t>290173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>115783</t>
+          <t>121777</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99559</t>
+          <t>104443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132688</t>
+          <t>140214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>194253</t>
+          <t>203103</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176033</t>
+          <t>185020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>215108</t>
+          <t>221594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>310036</t>
+          <t>324880</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>287211</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>333778</t>
+          <t>350198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>455204</t>
+          <t>496727</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>455204</t>
+          <t>496727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>455204</t>
+          <t>496727</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>702974</t>
+          <t>761909</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>702974</t>
+          <t>761909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>702974</t>
+          <t>761909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1158178</t>
+          <t>1258636</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1158178</t>
+          <t>1258636</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1158178</t>
+          <t>1258636</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>165416</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120900</t>
+          <t>140108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178249</t>
+          <t>196706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>142379</t>
+          <t>155052</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101287</t>
+          <t>133369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171808</t>
+          <t>178832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>289501</t>
+          <t>320468</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228523</t>
+          <t>287290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331625</t>
+          <t>357348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>442573</t>
+          <t>476366</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>403911</t>
+          <t>440969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488124</t>
+          <t>522258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>428826</t>
+          <t>474917</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280846</t>
+          <t>442035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>498727</t>
+          <t>509375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>871399</t>
+          <t>951283</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>686993</t>
+          <t>894817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>942233</t>
+          <t>1006114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>477267</t>
+          <t>500936</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>439488</t>
+          <t>458316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>520644</t>
+          <t>540444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>712998</t>
+          <t>526054</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550694</t>
+          <t>492000</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1117043</t>
+          <t>560472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1190265</t>
+          <t>1026990</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1031692</t>
+          <t>971527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1669641</t>
+          <t>1078215</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>249136</t>
+          <t>271365</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220897</t>
+          <t>243053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280394</t>
+          <t>304947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>236074</t>
+          <t>261543</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165445</t>
+          <t>237996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277421</t>
+          <t>287434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>485211</t>
+          <t>532908</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388092</t>
+          <t>491778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534545</t>
+          <t>572367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259921</t>
+          <t>279028</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233107</t>
+          <t>247995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289083</t>
+          <t>311796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>336125</t>
+          <t>377653</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230083</t>
+          <t>347724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391915</t>
+          <t>409641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>596045</t>
+          <t>656681</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>479764</t>
+          <t>609968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>650673</t>
+          <t>698547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1576019</t>
+          <t>1693111</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1576019</t>
+          <t>1693111</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1576019</t>
+          <t>1693111</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1856402</t>
+          <t>1795219</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1856402</t>
+          <t>1795219</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1856402</t>
+          <t>1795219</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3432421</t>
+          <t>3488330</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3432421</t>
+          <t>3488330</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3432421</t>
+          <t>3488330</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50795</t>
+          <t>53088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>71304</t>
+          <t>78641</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57333</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90740</t>
+          <t>97020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>139967</t>
+          <t>156918</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117491</t>
+          <t>136167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160760</t>
+          <t>182231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>138464</t>
+          <t>156940</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121224</t>
+          <t>138576</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157771</t>
+          <t>179588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>278431</t>
+          <t>313858</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251978</t>
+          <t>284133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310977</t>
+          <t>343280</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178444</t>
+          <t>194951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155405</t>
+          <t>171076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201230</t>
+          <t>217834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182394</t>
+          <t>199824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164680</t>
+          <t>178540</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201189</t>
+          <t>221007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>360839</t>
+          <t>394775</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326813</t>
+          <t>365004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>389063</t>
+          <t>426277</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86986</t>
+          <t>96074</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71528</t>
+          <t>79507</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106095</t>
+          <t>116510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>96695</t>
+          <t>111526</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81731</t>
+          <t>94962</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111715</t>
+          <t>128599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>183680</t>
+          <t>207600</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161458</t>
+          <t>182400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211061</t>
+          <t>232237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>96112</t>
+          <t>107021</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79271</t>
+          <t>89377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113937</t>
+          <t>126531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>131145</t>
+          <t>146119</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113372</t>
+          <t>129134</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>149443</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>227257</t>
+          <t>253140</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202230</t>
+          <t>225680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>256048</t>
+          <t>281207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>534456</t>
+          <t>592920</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>534456</t>
+          <t>592920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>534456</t>
+          <t>592920</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>587054</t>
+          <t>655095</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>587054</t>
+          <t>655095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>587054</t>
+          <t>655095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1121511</t>
+          <t>1248015</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1121511</t>
+          <t>1248015</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1121511</t>
+          <t>1248015</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>213024</t>
+          <t>242233</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182664</t>
+          <t>209785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246138</t>
+          <t>275933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>209403</t>
+          <t>226643</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163118</t>
+          <t>203219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238021</t>
+          <t>255296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>422427</t>
+          <t>468877</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369171</t>
+          <t>427623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>468492</t>
+          <t>513032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>674731</t>
+          <t>736173</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621943</t>
+          <t>685494</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>724347</t>
+          <t>787169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>694278</t>
+          <t>769688</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>539728</t>
+          <t>726272</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>760157</t>
+          <t>812450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1369009</t>
+          <t>1505861</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1201260</t>
+          <t>1437037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1443723</t>
+          <t>1571787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>23,97%</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>769271</t>
+          <t>821930</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>720647</t>
+          <t>776828</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>819309</t>
+          <t>881137</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1101985</t>
+          <t>956334</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>941356</t>
+          <t>913197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1615421</t>
+          <t>999304</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1871256</t>
+          <t>1778264</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1706057</t>
+          <t>1708428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2386762</t>
+          <t>1845002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>436837</t>
+          <t>474596</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>399056</t>
+          <t>432106</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>475463</t>
+          <t>511942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>479242</t>
+          <t>532683</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>367927</t>
+          <t>500299</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>525659</t>
+          <t>567535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>916078</t>
+          <t>1007278</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>801552</t>
+          <t>954021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>979321</t>
+          <t>1058988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>471816</t>
+          <t>507827</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>432255</t>
+          <t>469828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>506763</t>
+          <t>548100</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>661523</t>
+          <t>726874</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>511344</t>
+          <t>687615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>721810</t>
+          <t>768585</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1133339</t>
+          <t>1234701</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1001107</t>
+          <t>1180419</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1198857</t>
+          <t>1300258</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2565679</t>
+          <t>2782759</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2565679</t>
+          <t>2782759</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2565679</t>
+          <t>2782759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3146431</t>
+          <t>3212223</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3146431</t>
+          <t>3212223</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3146431</t>
+          <t>3212223</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5712110</t>
+          <t>5994981</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5712110</t>
+          <t>5994981</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5712110</t>
+          <t>5994981</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
